--- a/sheets/대금율보/검수/뽕따러가세.xlsx
+++ b/sheets/대금율보/검수/뽕따러가세.xlsx
@@ -3499,17 +3499,9 @@
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="26"/>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F8" s="21"/>
       <c r="G8" s="26"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
@@ -3533,11 +3525,7 @@
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L8" s="21"/>
       <c r="M8" s="26"/>
     </row>
     <row r="9" ht="56" customHeight="1">
@@ -3862,8 +3850,7 @@
       <c r="C14" s="26"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-‹</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="E14" s="26"/>

--- a/sheets/대금율보/검수/뽕따러가세.xlsx
+++ b/sheets/대금율보/검수/뽕따러가세.xlsx
@@ -3168,24 +3168,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="48.19" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="71.62" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="71.62" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
       <c r="L4" s="21"/>
       <c r="M4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="71.62" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="71.62" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
       <c r="L6" s="21"/>
       <c r="M6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="71.62" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
       <c r="L7" s="21"/>
       <c r="M7" s="25"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="71.62" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
       <c r="L8" s="21"/>
       <c r="M8" s="26"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="71.62" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="71.62" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="71.62" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="71.62" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="71.62" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="25"/>
@@ -3839,7 +3839,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="71.62" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3889,6 +3889,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="83"/>
 </worksheet>
 </file>